--- a/SA_Annual_Compliance_Tracker.xlsx
+++ b/SA_Annual_Compliance_Tracker.xlsx
@@ -21,19 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sole proprietor'!$A$5:$Q$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Sole proprietor'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Partnership'!$A$5:$Q$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Partnership'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Company &amp; CC'!$A$5:$Q$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Company &amp; CC'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Trust'!$A$5:$Q$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Trust'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'NPO Overlay'!$A$5:$Q$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'NPO Overlay'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Employer Overlay'!$A$5:$Q$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Employer Overlay'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Common Controls'!$A$5:$Q$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Common Controls'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
@@ -1350,6 +1343,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -1468,8 +1462,8 @@
           <t>Compare profile to official records and correct discrepancies promptly; use each authority’s change-notification deadline.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Entity profile, tax registrations, representative appointment and change-submission receipts.</t>
@@ -1483,8 +1477,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-PIT; SRC-SARS-CIT; SRC-SARS-TRUST; SRC-CIPC-AR</t>
@@ -1526,8 +1520,8 @@
           <t>Review current notices, access controls, retention, incident response and regulator/contact details; schedule event-driven statutory duties separately.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Review checklist, current notices, access/retention controls and incident log (store securely).</t>
@@ -1541,9 +1535,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
+      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="23">
         <f>IF(K7="","",K7-TODAY())</f>
         <v/>
@@ -1580,8 +1574,8 @@
           <t>Enter each regulator/municipality’s real expiry and renewal deadline; do not assume a single national annual date.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Current licences, permits, registrations, certificates, renewal submissions and receipts.</t>
@@ -1595,9 +1589,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
-      <c r="P8" s="19" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
+      <c r="P8" s="19" t="n"/>
       <c r="Q8" s="22">
         <f>IF(K8="","",K8-TODAY())</f>
         <v/>
@@ -1634,8 +1628,8 @@
           <t>Update annual dates after the relevant authority publishes its current filing windows; record reviewer sign-off.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Dated applicability review, current authority notices and updated due-date entries.</t>
@@ -1649,16 +1643,15 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="23">
         <f>IF(K9="","",K9-TODAY())</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q9"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -1739,6 +1732,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
@@ -1832,14 +1827,14 @@
           <t>CUSTOM-01</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
       <c r="J6" s="21" t="n"/>
       <c r="K6" s="21" t="n"/>
       <c r="L6" s="21" t="n"/>
@@ -1848,9 +1843,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
+      <c r="P6" s="20" t="n"/>
       <c r="Q6" s="4">
         <f>IF(K6="","",K6-TODAY())</f>
         <v/>
@@ -1862,14 +1857,14 @@
           <t>CUSTOM-02</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
       <c r="J7" s="21" t="n"/>
       <c r="K7" s="21" t="n"/>
       <c r="L7" s="21" t="n"/>
@@ -1878,9 +1873,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
+      <c r="P7" s="20" t="n"/>
       <c r="Q7" s="4">
         <f>IF(K7="","",K7-TODAY())</f>
         <v/>
@@ -1892,14 +1887,14 @@
           <t>CUSTOM-03</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr"/>
-      <c r="C8" s="20" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr"/>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="20" t="inlineStr"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
       <c r="J8" s="21" t="n"/>
       <c r="K8" s="21" t="n"/>
       <c r="L8" s="21" t="n"/>
@@ -1908,9 +1903,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
-      <c r="P8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
+      <c r="P8" s="20" t="n"/>
       <c r="Q8" s="4">
         <f>IF(K8="","",K8-TODAY())</f>
         <v/>
@@ -1922,14 +1917,14 @@
           <t>CUSTOM-04</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
       <c r="J9" s="21" t="n"/>
       <c r="K9" s="21" t="n"/>
       <c r="L9" s="21" t="n"/>
@@ -1938,9 +1933,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
+      <c r="P9" s="20" t="n"/>
       <c r="Q9" s="4">
         <f>IF(K9="","",K9-TODAY())</f>
         <v/>
@@ -1952,14 +1947,14 @@
           <t>CUSTOM-05</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
       <c r="J10" s="21" t="n"/>
       <c r="K10" s="21" t="n"/>
       <c r="L10" s="21" t="n"/>
@@ -1968,9 +1963,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
+      <c r="P10" s="20" t="n"/>
       <c r="Q10" s="4">
         <f>IF(K10="","",K10-TODAY())</f>
         <v/>
@@ -1982,14 +1977,14 @@
           <t>CUSTOM-06</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr"/>
-      <c r="C11" s="20" t="inlineStr"/>
-      <c r="D11" s="20" t="inlineStr"/>
-      <c r="E11" s="20" t="inlineStr"/>
-      <c r="F11" s="20" t="inlineStr"/>
-      <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
-      <c r="I11" s="20" t="inlineStr"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
       <c r="J11" s="21" t="n"/>
       <c r="K11" s="21" t="n"/>
       <c r="L11" s="21" t="n"/>
@@ -1998,9 +1993,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N11" s="20" t="inlineStr"/>
-      <c r="O11" s="20" t="inlineStr"/>
-      <c r="P11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="20" t="n"/>
+      <c r="P11" s="20" t="n"/>
       <c r="Q11" s="4">
         <f>IF(K11="","",K11-TODAY())</f>
         <v/>
@@ -2012,14 +2007,14 @@
           <t>CUSTOM-07</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
       <c r="J12" s="21" t="n"/>
       <c r="K12" s="21" t="n"/>
       <c r="L12" s="21" t="n"/>
@@ -2028,9 +2023,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
+      <c r="N12" s="20" t="n"/>
+      <c r="O12" s="20" t="n"/>
+      <c r="P12" s="20" t="n"/>
       <c r="Q12" s="4">
         <f>IF(K12="","",K12-TODAY())</f>
         <v/>
@@ -2042,14 +2037,14 @@
           <t>CUSTOM-08</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
       <c r="J13" s="21" t="n"/>
       <c r="K13" s="21" t="n"/>
       <c r="L13" s="21" t="n"/>
@@ -2058,9 +2053,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
+      <c r="N13" s="20" t="n"/>
+      <c r="O13" s="20" t="n"/>
+      <c r="P13" s="20" t="n"/>
       <c r="Q13" s="4">
         <f>IF(K13="","",K13-TODAY())</f>
         <v/>
@@ -2072,14 +2067,14 @@
           <t>CUSTOM-09</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
-      <c r="H14" s="20" t="inlineStr"/>
-      <c r="I14" s="20" t="inlineStr"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
       <c r="J14" s="21" t="n"/>
       <c r="K14" s="21" t="n"/>
       <c r="L14" s="21" t="n"/>
@@ -2088,9 +2083,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N14" s="20" t="inlineStr"/>
-      <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
+      <c r="N14" s="20" t="n"/>
+      <c r="O14" s="20" t="n"/>
+      <c r="P14" s="20" t="n"/>
       <c r="Q14" s="4">
         <f>IF(K14="","",K14-TODAY())</f>
         <v/>
@@ -2102,14 +2097,14 @@
           <t>CUSTOM-10</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
       <c r="J15" s="21" t="n"/>
       <c r="K15" s="21" t="n"/>
       <c r="L15" s="21" t="n"/>
@@ -2118,9 +2113,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N15" s="20" t="inlineStr"/>
-      <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
+      <c r="N15" s="20" t="n"/>
+      <c r="O15" s="20" t="n"/>
+      <c r="P15" s="20" t="n"/>
       <c r="Q15" s="4">
         <f>IF(K15="","",K15-TODAY())</f>
         <v/>
@@ -2132,14 +2127,14 @@
           <t>CUSTOM-11</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
-      <c r="I16" s="20" t="inlineStr"/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
       <c r="J16" s="21" t="n"/>
       <c r="K16" s="21" t="n"/>
       <c r="L16" s="21" t="n"/>
@@ -2148,9 +2143,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N16" s="20" t="inlineStr"/>
-      <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
+      <c r="N16" s="20" t="n"/>
+      <c r="O16" s="20" t="n"/>
+      <c r="P16" s="20" t="n"/>
       <c r="Q16" s="4">
         <f>IF(K16="","",K16-TODAY())</f>
         <v/>
@@ -2162,14 +2157,14 @@
           <t>CUSTOM-12</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr"/>
-      <c r="C17" s="20" t="inlineStr"/>
-      <c r="D17" s="20" t="inlineStr"/>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="20" t="inlineStr"/>
-      <c r="G17" s="20" t="inlineStr"/>
-      <c r="H17" s="20" t="inlineStr"/>
-      <c r="I17" s="20" t="inlineStr"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
       <c r="J17" s="21" t="n"/>
       <c r="K17" s="21" t="n"/>
       <c r="L17" s="21" t="n"/>
@@ -2178,9 +2173,9 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N17" s="20" t="inlineStr"/>
-      <c r="O17" s="20" t="inlineStr"/>
-      <c r="P17" s="20" t="inlineStr"/>
+      <c r="N17" s="20" t="n"/>
+      <c r="O17" s="20" t="n"/>
+      <c r="P17" s="20" t="n"/>
       <c r="Q17" s="4">
         <f>IF(K17="","",K17-TODAY())</f>
         <v/>
@@ -2246,6 +2241,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -2746,6 +2742,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -3311,6 +3308,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="42" t="inlineStr">
         <is>
@@ -3327,6 +3325,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="33" t="inlineStr">
         <is>
@@ -3384,13 +3383,14 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Business / entity legal name</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr"/>
+      <c r="B4" s="9" t="n"/>
       <c r="C4" s="29" t="n"/>
       <c r="D4" s="29" t="n"/>
     </row>
@@ -3400,7 +3400,7 @@
           <t>Trading name (if different)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr"/>
+      <c r="B5" s="9" t="n"/>
       <c r="C5" s="29" t="n"/>
       <c r="D5" s="29" t="n"/>
     </row>
@@ -3410,7 +3410,7 @@
           <t>Legal form</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
+      <c r="B6" s="9" t="n"/>
       <c r="C6" s="29" t="n"/>
       <c r="D6" s="29" t="n"/>
     </row>
@@ -3420,7 +3420,7 @@
           <t>Registration / trust / NPO number(s)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
+      <c r="B7" s="9" t="n"/>
       <c r="C7" s="29" t="n"/>
       <c r="D7" s="29" t="n"/>
     </row>
@@ -3430,7 +3430,7 @@
           <t>Tracker year</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
+      <c r="B8" s="9" t="n"/>
       <c r="C8" s="29" t="n"/>
       <c r="D8" s="29" t="n"/>
     </row>
@@ -3440,7 +3440,7 @@
           <t>Financial year-end (dd/mm/yyyy)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
+      <c r="B9" s="9" t="n"/>
       <c r="C9" s="29" t="n"/>
       <c r="D9" s="29" t="n"/>
     </row>
@@ -3450,7 +3450,7 @@
           <t>CIPC incorporation anniversary (if relevant)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
+      <c r="B10" s="9" t="n"/>
       <c r="C10" s="29" t="n"/>
       <c r="D10" s="29" t="n"/>
     </row>
@@ -3460,7 +3460,7 @@
           <t>SARS income-tax reference(s)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
+      <c r="B11" s="9" t="n"/>
       <c r="C11" s="29" t="n"/>
       <c r="D11" s="29" t="n"/>
     </row>
@@ -3470,7 +3470,7 @@
           <t>VAT registered? (Yes/No/Review)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr"/>
+      <c r="B12" s="9" t="n"/>
       <c r="C12" s="29" t="n"/>
       <c r="D12" s="29" t="n"/>
     </row>
@@ -3480,7 +3480,7 @@
           <t>VAT tax period / category</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="n"/>
       <c r="C13" s="29" t="n"/>
       <c r="D13" s="29" t="n"/>
     </row>
@@ -3490,7 +3490,7 @@
           <t>Employer with employees? (Yes/No/Review)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr"/>
+      <c r="B14" s="9" t="n"/>
       <c r="C14" s="29" t="n"/>
       <c r="D14" s="29" t="n"/>
     </row>
@@ -3500,7 +3500,7 @@
           <t>NPO Directorate registered? (Yes/No/Review)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="n"/>
       <c r="C15" s="29" t="n"/>
       <c r="D15" s="29" t="n"/>
     </row>
@@ -3510,7 +3510,7 @@
           <t>PBO / tax-exempt status (Yes/No/Review)</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr"/>
+      <c r="B16" s="9" t="n"/>
       <c r="C16" s="29" t="n"/>
       <c r="D16" s="29" t="n"/>
     </row>
@@ -3520,7 +3520,7 @@
           <t>Trust Master reference (if relevant)</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
       <c r="C17" s="29" t="n"/>
       <c r="D17" s="29" t="n"/>
     </row>
@@ -3530,7 +3530,7 @@
           <t>Partnership IT3(BO) representative (if relevant)</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr"/>
+      <c r="B18" s="9" t="n"/>
       <c r="C18" s="29" t="n"/>
       <c r="D18" s="29" t="n"/>
     </row>
@@ -3540,7 +3540,7 @@
           <t>Primary compliance lead</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr"/>
+      <c r="B19" s="9" t="n"/>
       <c r="C19" s="29" t="n"/>
       <c r="D19" s="29" t="n"/>
     </row>
@@ -3550,7 +3550,7 @@
           <t>Reviewer / approver</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr"/>
+      <c r="B20" s="9" t="n"/>
       <c r="C20" s="29" t="n"/>
       <c r="D20" s="29" t="n"/>
     </row>
@@ -3560,10 +3560,12 @@
           <t>Document repository / evidence root</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr"/>
+      <c r="B21" s="9" t="n"/>
       <c r="C21" s="29" t="n"/>
       <c r="D21" s="29" t="n"/>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -3600,7 +3602,7 @@
         </is>
       </c>
       <c r="C26" s="29" t="n"/>
-      <c r="D26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -3614,7 +3616,7 @@
         </is>
       </c>
       <c r="C27" s="29" t="n"/>
-      <c r="D27" s="9" t="inlineStr"/>
+      <c r="D27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3628,7 +3630,7 @@
         </is>
       </c>
       <c r="C28" s="29" t="n"/>
-      <c r="D28" s="9" t="inlineStr"/>
+      <c r="D28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -3642,7 +3644,7 @@
         </is>
       </c>
       <c r="C29" s="29" t="n"/>
-      <c r="D29" s="9" t="inlineStr"/>
+      <c r="D29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3656,7 +3658,7 @@
         </is>
       </c>
       <c r="C30" s="29" t="n"/>
-      <c r="D30" s="9" t="inlineStr"/>
+      <c r="D30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -3670,7 +3672,7 @@
         </is>
       </c>
       <c r="C31" s="29" t="n"/>
-      <c r="D31" s="9" t="inlineStr"/>
+      <c r="D31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3684,7 +3686,7 @@
         </is>
       </c>
       <c r="C32" s="29" t="n"/>
-      <c r="D32" s="9" t="inlineStr"/>
+      <c r="D32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -3698,8 +3700,10 @@
         </is>
       </c>
       <c r="C33" s="29" t="n"/>
-      <c r="D33" s="9" t="inlineStr"/>
-    </row>
+      <c r="D33" s="9" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
@@ -3804,6 +3808,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -3922,8 +3927,8 @@
           <t>Use the current SARS filing-season notice and the taxpayer’s eFiling deadline. Tax year normally runs 1 March to 28/29 February; do not reuse a prior-year filing date.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Filed ITR12, assessment, schedules and supporting tax workpapers.</t>
@@ -3937,8 +3942,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-PIT</t>
@@ -3980,8 +3985,8 @@
           <t>Confirm status and current SARS due dates for the tax year; enter the actual dates in Due date.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>IRP6 submissions, estimates, payment confirmations and supporting calculations.</t>
@@ -3995,8 +4000,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
           <t>SRC-SARS-PIT</t>
@@ -4038,8 +4043,8 @@
           <t>Use the assigned VAT category and current VAT201 deadline. As at 1 April 2026 SARS lists compulsory registration threshold R2.3m and voluntary threshold R120,000; recheck current law and SARS guidance.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
           <t>VAT201s, VAT control reconciliations, invoices, source documents and payment/refund records.</t>
@@ -4053,8 +4058,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
       <c r="P8" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-VAT</t>
@@ -4096,8 +4101,8 @@
           <t>Enter each authority’s actual renewal date; obligations differ by activity and municipality.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Current licence/permit, renewal submission and payment proof.</t>
@@ -4111,16 +4116,15 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="23">
         <f>IF(K9="","",K9-TODAY())</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q9"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -4208,6 +4212,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -4326,8 +4331,8 @@
           <t>Submit the IT3(BO) annually and before the related partners submit ITR12s. SARS says it may be submitted/updated during the year; no timing penalty is currently stated on the guidance page.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Submitted IT3(BO), SARS acknowledgement/unique number, current partner details and change log.</t>
@@ -4341,8 +4346,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-PART-BO</t>
@@ -4384,8 +4389,8 @@
           <t>Use each partner’s current SARS filing-season deadline; the partnership IT3(BO) unique number is used in the ITR12 process.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Each partner’s ITR12, profit allocation and tax workpapers; IT3(BO) unique number reference.</t>
@@ -4399,8 +4404,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
           <t>SRC-SARS-PIT; SRC-SARS-PART-BO</t>
@@ -4442,8 +4447,8 @@
           <t>Confirm each partner’s status and SARS dates for the relevant year; record separate partner-specific due dates where needed.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
           <t>IRP6s, calculations, payments and partner allocation schedule.</t>
@@ -4457,8 +4462,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
       <c r="P8" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-PIT</t>
@@ -4500,8 +4505,8 @@
           <t>Use the assigned VAT category and current VAT201 deadline. As at 1 April 2026 SARS lists compulsory registration threshold R2.3m and voluntary threshold R120,000; recheck current law and SARS guidance.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>VAT201s, VAT reconciliations, invoices and payment/refund records.</t>
@@ -4515,8 +4520,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
       <c r="P9" s="4" t="inlineStr">
         <is>
           <t>SRC-SARS-VAT</t>
@@ -4558,8 +4563,8 @@
           <t>Review before tax close; admissions, exits, profit-share changes and dissolution require prompt legal/tax follow-through.</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Current signed partnership agreement, partner resolutions/mandates and allocation schedule.</t>
@@ -4573,8 +4578,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
       <c r="P10" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-PART-BO</t>
@@ -4586,7 +4591,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q10"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -4674,6 +4678,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -4792,8 +4797,8 @@
           <t>Company: file within 30 business days after the annual-return due point tied to incorporation anniversary. CC: filing window runs from first day of anniversary month through the following month. This is not the financial year-end.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
           <t>CIPC annual-return certificate/receipt, BO submission receipt, AFS/FAS filing and compliance checklist.</t>
@@ -4807,8 +4812,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>SRC-CIPC-AR; SRC-CIPC-BO</t>
@@ -4850,8 +4855,8 @@
           <t>Companies: prepare within six months after financial year-end (Companies Act s30). CCs: current consolidated CC Act s58 also sets six months. Confirm audit/review/accounting-officer rules for the specific entity.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Approved and signed AFS, auditor/independent-review/accounting-officer report as applicable, and board/member approval evidence.</t>
@@ -4865,8 +4870,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
           <t>SRC-COMPANIES-ACT; SRC-CC-ACT; SRC-CIPC-AR</t>
@@ -4908,8 +4913,8 @@
           <t>Use SARS eFiling/notice for the company’s exact deadline; do not confuse SARS filing dates with CIPC anniversary dates.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Filed ITR14, assessment, tax computation and payment/arrangement evidence.</t>
@@ -4923,8 +4928,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
       <c r="P8" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-CIT</t>
@@ -4966,8 +4971,8 @@
           <t>SARS guidance: first payment six months after start of assessment year; second on/before assessment-year end; optional top-up six months after year-end (February year-end rules differ). Verify current dates and exception status.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>IRP6 declarations, income estimates, payment confirmations and tax workpapers.</t>
@@ -4981,8 +4986,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
       <c r="P9" s="4" t="inlineStr">
         <is>
           <t>SRC-SARS-CIT</t>
@@ -5024,8 +5029,8 @@
           <t>Use assigned VAT category and current VAT201 deadline. As at 1 April 2026 SARS lists compulsory registration threshold R2.3m and voluntary threshold R120,000; recheck current guidance.</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="inlineStr">
         <is>
           <t>VAT201s, reconciliations, invoices and payment/refund records.</t>
@@ -5039,8 +5044,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
       <c r="P10" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-VAT</t>
@@ -5082,8 +5087,8 @@
           <t>Complete at year-end and before CIPC annual return; reconcile CIPC, SARS, securities/member and internal records.</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Register review checklist, current securities/member and director records, BO evidence, change filings and accounting-record index.</t>
@@ -5097,8 +5102,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N11" s="20" t="inlineStr"/>
-      <c r="O11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="20" t="n"/>
       <c r="P11" s="4" t="inlineStr">
         <is>
           <t>SRC-CIPC-AR; SRC-CIPC-BO; SRC-COMPANIES-ACT</t>
@@ -5110,7 +5115,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q11"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -5198,6 +5202,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -5316,8 +5321,8 @@
           <t>Use the current SARS Trust Filing Season notice and eFiling deadline; dates and form requirements are updated annually.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Filed ITR12T, assessment, tax computation, IT3(t) data and supporting schedules.</t>
@@ -5331,8 +5336,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-TRUST</t>
@@ -5374,8 +5379,8 @@
           <t>Use current SARS provisional-tax dates for the assessment year; enter actual instalment dates separately.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>IRP6 submissions, calculations and payment confirmations.</t>
@@ -5389,8 +5394,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
           <t>SRC-SARS-TRUST</t>
@@ -5432,8 +5437,8 @@
           <t>Keep the register accurate and up to date; lodge with the Master and update after changes within a reasonable time. SARS disclosure alone does not satisfy the Master filing duty.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Master submission/acknowledgement, current BO register, supporting IDs and change log (store securely).</t>
@@ -5447,8 +5452,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
       <c r="P8" s="19" t="inlineStr">
         <is>
           <t>SRC-JUSTICE-TRUST-BO</t>
@@ -5490,8 +5495,8 @@
           <t>Complete before annual accounts and ITR12T; update bank, Master and SARS particulars promptly when changed.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Trustee resolutions, current letters of authority, accounts, asset/liability schedules and deed-compliance checklist.</t>
@@ -5505,8 +5510,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
       <c r="P9" s="4" t="inlineStr">
         <is>
           <t>SRC-SARS-TRUST; SRC-JUSTICE-TRUST-BO</t>
@@ -5548,8 +5553,8 @@
           <t>Use assigned VAT category and current VAT201 deadline; review 2026 registration thresholds and special rules.</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="inlineStr">
         <is>
           <t>VAT201s, reconciliations, invoices and payment/refund records.</t>
@@ -5563,8 +5568,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
       <c r="P10" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-VAT</t>
@@ -5576,7 +5581,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q10"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -5664,6 +5668,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -5782,8 +5787,8 @@
           <t>Draw up within six months after financial year-end under DSD guidance.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Income/expenditure statement, balance sheet, accounting records and approval evidence.</t>
@@ -5797,8 +5802,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>SRC-DSD-NPO; SRC-NPO-ACT</t>
@@ -5840,8 +5845,8 @@
           <t>Within two months after drawing up the financial statements, per DSD guidance.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Accounting officer’s signed report and supporting engagement/workpapers.</t>
@@ -5855,8 +5860,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
           <t>SRC-DSD-NPO; SRC-NPO-ACT</t>
@@ -5898,8 +5903,8 @@
           <t>Within nine months after financial year-end under NPO Act s18; enter the actual due date from the NPO financial year-end.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Submission receipt and copies of narrative report, financial statements and accounting officer report.</t>
@@ -5913,8 +5918,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
       <c r="P8" s="19" t="inlineStr">
         <is>
           <t>SRC-NPO-ACT; SRC-DSD-NPO</t>
@@ -5956,8 +5961,8 @@
           <t>DSD states records must be preserved for at least five years; confirm any longer retention rule applicable to the underlying legal form or other laws.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Indexed accounting records, vouchers, member subscriptions/levies, annual statements and reports.</t>
@@ -5971,8 +5976,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
       <c r="P9" s="4" t="inlineStr">
         <is>
           <t>SRC-DSD-NPO; SRC-NPO-ACT</t>
@@ -6014,8 +6019,8 @@
           <t>Office-bearer details within one month after appointment/election (including re-election even with no change); address change notice within one month before the new service address takes effect.</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Filed notices, resolutions/election records and Directorate acknowledgements.</t>
@@ -6029,8 +6034,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
       <c r="P10" s="19" t="inlineStr">
         <is>
           <t>SRC-NPO-ACT; SRC-DSD-NPO</t>
@@ -6072,8 +6077,8 @@
           <t>Review founding document and SARS tax status; determine return type/deadline from the underlying form (company, trust or individual/association) and current SARS notices.</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Current founding document, registration certificate, tax-exemption/PBO ruling if any, SARS submissions and funding-condition log.</t>
@@ -6087,8 +6092,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N11" s="20" t="inlineStr"/>
-      <c r="O11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="20" t="n"/>
       <c r="P11" s="4" t="inlineStr">
         <is>
           <t>SRC-DSD-NPO; SRC-SARS-CIT; SRC-SARS-TRUST; SRC-SARS-PIT</t>
@@ -6100,7 +6105,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q11"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -6188,6 +6192,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
@@ -6306,8 +6311,8 @@
           <t>Within seven days after month-end; if the 7th is a weekend or public holiday, file/pay by the last business day before.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
           <t>EMP201, payroll reconciliation, payment confirmation and PRN allocation evidence.</t>
@@ -6321,8 +6326,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="n"/>
+      <c r="O6" s="20" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-EMP201</t>
@@ -6364,8 +6369,8 @@
           <t>Interim period: 1 March–31 August; annual period: 1 March–28/29 February. Submit by the current SARS/Gazette dates; windows vary by year.</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>EMP501 acknowledgements, IRP5/IT3(a) certificates, EMP201/payment reconciliation and correction evidence.</t>
@@ -6379,8 +6384,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="20" t="n"/>
       <c r="P7" s="4" t="inlineStr">
         <is>
           <t>SRC-SARS-EMP501</t>
@@ -6422,8 +6427,8 @@
           <t>Department guidance says register within seven days after appointing employee(s); verify current category-specific rules.</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Registration and contract account number; mutual-association confirmation if applicable.</t>
@@ -6437,8 +6442,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="20" t="n"/>
       <c r="P8" s="19" t="inlineStr">
         <is>
           <t>SRC-DOEL-CF</t>
@@ -6480,8 +6485,8 @@
           <t>Submit within the current ROE period/deadline notified by the Compensation Fund; do not rely on historical sample dates.</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>ROE submission receipt, payroll/earnings support, assessment and payment proof; Letter of Good Standing if needed.</t>
@@ -6495,8 +6500,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="20" t="n"/>
       <c r="P9" s="4" t="inlineStr">
         <is>
           <t>SRC-DOEL-CF</t>
@@ -6538,8 +6543,8 @@
           <t>SARS states EMP501 supporting declarations/material must be kept for five years; Department guidance states Compensation Fund records for four years. Apply any longer law-specific period.</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
       <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Payroll registers, time/earnings records, EMP201/EMP501, tax certificates, ROE and assessments.</t>
@@ -6553,8 +6558,8 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
       <c r="P10" s="19" t="inlineStr">
         <is>
           <t>SRC-SARS-EMP501; SRC-DOEL-CF</t>
@@ -6596,8 +6601,8 @@
           <t>Set review date before the new operating year; schedule any statutory inspections, appointments or training separately at the frequency required by applicable law.</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Risk assessments, appointments, training records, incident log, policies and inspection evidence.</t>
@@ -6611,16 +6616,15 @@
           <t>Needs assessment</t>
         </is>
       </c>
-      <c r="N11" s="20" t="inlineStr"/>
-      <c r="O11" s="20" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="20" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="23">
         <f>IF(K11="","",K11-TODAY())</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Q11"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
